--- a/results/Int Task Remove ACC -0.8/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC -0.8/Rando_10_permute.xlsx
@@ -440,237 +440,237 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6609928110316128</v>
+        <v>0.6762565770959297</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6652744969285567</v>
+        <v>0.668822788660248</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6692900431792921</v>
+        <v>0.6862586664165167</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6570533046797938</v>
+        <v>0.6760259701127664</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6574089866368761</v>
+        <v>0.6434148026231633</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6566596027732533</v>
+        <v>0.6430346031285799</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6555030145911327</v>
+        <v>0.6394838241104752</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6465704584282055</v>
+        <v>0.6394838241104752</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6574359914607903</v>
+        <v>0.6398014861180992</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6578542109048322</v>
+        <v>0.6398014861180992</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6865578514393571</v>
+        <v>0.6411101540980531</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6719589015006154</v>
+        <v>0.6514789405012664</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6742205555034411</v>
+        <v>0.6525840063219714</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6835713311104099</v>
+        <v>0.6473713646532439</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.678969495919429</v>
+        <v>0.6535185153600596</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6792871579270529</v>
+        <v>0.6523999471273974</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6754371938861079</v>
+        <v>0.6456149851189208</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7152504768483381</v>
+        <v>0.6416999963046031</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7155436213184607</v>
+        <v>0.6197418765225746</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7172459912049552</v>
+        <v>0.6239365073950578</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7035620073396269</v>
+        <v>0.6234667655896006</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7170178715082052</v>
+        <v>0.6155767377604189</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8083695055843133</v>
+        <v>0.6054790655762403</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8087877250283551</v>
+        <v>0.6210089712867657</v>
       </c>
     </row>
     <row r="26">
@@ -680,647 +680,647 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8059913044466995</v>
+        <v>0.6169173851371135</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7500163450250008</v>
+        <v>0.6160784589626168</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7839081096907521</v>
+        <v>0.6115281461330513</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7656848281214024</v>
+        <v>0.6125571720548397</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7534271253507074</v>
+        <v>0.6003399765200162</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7534271253507074</v>
+        <v>0.6053109960800366</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7351253165960278</v>
+        <v>0.605349016029495</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7291057281495441</v>
+        <v>0.6077137147551515</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7151371276532239</v>
+        <v>0.6069042806909823</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7377856470782203</v>
+        <v>0.608288988569853</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6976998285904334</v>
+        <v>0.6005926137542674</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7021446094107547</v>
+        <v>0.6005926137542674</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6939969697744955</v>
+        <v>0.5922904070337618</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6776746856780627</v>
+        <v>0.6025991432364286</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6788582786840975</v>
+        <v>0.642691002276933</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6967688728186499</v>
+        <v>0.6682830475085918</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6677596513819364</v>
+        <v>0.6403028519936667</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6700998325700918</v>
+        <v>0.6335939298841067</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6686120799683901</v>
+        <v>0.6317995304003252</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5986145104025424</v>
+        <v>0.603808319759856</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5982968483949186</v>
+        <v>0.6189630005486244</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6149577587701719</v>
+        <v>0.6252522819076207</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6145615695772182</v>
+        <v>0.5848111367893822</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5744405737530167</v>
+        <v>0.5957011873594684</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5416858543047111</v>
+        <v>0.5992004440161574</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.50146287973757</v>
+        <v>0.6027082285119774</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.50146287973757</v>
+        <v>0.6446751461813758</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4647576388119015</v>
+        <v>0.5875634968688617</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4671958901500616</v>
+        <v>0.5722091225137795</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4679417207473798</v>
+        <v>0.5894438853972126</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4330735185011469</v>
+        <v>0.5810020353109393</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.437903473388878</v>
+        <v>0.5550567954086114</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4250474005725022</v>
+        <v>0.5544975112922803</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4124194474528766</v>
+        <v>0.5725822154757539</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4055719479574404</v>
+        <v>0.5741840279258306</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4506458416835091</v>
+        <v>0.5832647552936561</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4116835660012109</v>
+        <v>0.546512611252768</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4253981079567581</v>
+        <v>0.5462329691946024</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4134815187512969</v>
+        <v>0.5887950589700076</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.3808188289002783</v>
+        <v>0.6089207593187962</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.3808188289002783</v>
+        <v>0.6171934739289745</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.3505823092819844</v>
+        <v>0.6322006941661052</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.3581926950530006</v>
+        <v>0.6197223335578997</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.3527949282098076</v>
+        <v>0.6177623518643278</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.3229311462268575</v>
+        <v>0.6177623518643278</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.3406317423228128</v>
+        <v>0.6358555838869322</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.3670150999604876</v>
+        <v>0.6366884695087112</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.3614982986960934</v>
+        <v>0.6363597923755433</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4036098343040857</v>
+        <v>0.5993514578340994</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4427668289798715</v>
+        <v>0.5265830512039887</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4660098098576135</v>
+        <v>0.5659361861797839</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4658577300597802</v>
+        <v>0.5654149220129112</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4771894516315177</v>
+        <v>0.5703749264473875</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4037238941524607</v>
+        <v>0.574546105762261</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4033372987785292</v>
+        <v>0.574546105762261</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4153015017524709</v>
+        <v>0.5538110202422475</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4153015017524709</v>
+        <v>0.5397255172845086</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.447261355528456</v>
+        <v>0.5902316445369241</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4490397653138671</v>
+        <v>0.5877663883748497</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4490397653138671</v>
+        <v>0.5708411149865402</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4843016694666405</v>
+        <v>0.5701297510723757</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4767243290722564</v>
+        <v>0.5026777414870847</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4767758514336718</v>
+        <v>0.4941104611002618</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4936830031638283</v>
+        <v>0.5040745304713905</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5002096427119666</v>
+        <v>0.5011505476294028</v>
       </c>
     </row>
   </sheetData>
